--- a/25_Lamya_Harsh_DS/mar28.xlsx
+++ b/25_Lamya_Harsh_DS/mar28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_Lamya_Harsh_DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD4AE0F-4A2F-49DE-B884-3A7639B5EC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66BAB37-FE37-418E-A9E9-A4088F29E37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{19844E60-48FB-4093-85C8-58AF9763D556}"/>
   </bookViews>
@@ -520,22 +520,37 @@
       <c r="C2">
         <v>32</v>
       </c>
+      <c r="D2">
+        <f>B2+C2</f>
+        <v>54</v>
+      </c>
       <c r="E2">
         <v>20</v>
       </c>
+      <c r="F2">
+        <f>D2+$E$2</f>
+        <v>74</v>
+      </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="H2">
         <v>55</v>
       </c>
+      <c r="I2" t="str">
+        <f>IF(H2&gt;=60, "Yes", "No")</f>
+        <v>No</v>
+      </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1">
+        <f>SUM(J2:J15)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -544,8 +559,20 @@
       <c r="C3">
         <v>31</v>
       </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D15" si="0">B3+C3</f>
+        <v>31</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F15" si="1">D3+$E$2</f>
+        <v>51</v>
+      </c>
       <c r="H3">
         <v>68</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I15" si="2">IF(H3&gt;=60, "Yes", "No")</f>
+        <v>Yes</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>14</v>
@@ -561,10 +588,25 @@
       <c r="C4">
         <v>30</v>
       </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
       <c r="H4">
         <v>77</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="I4" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
+      <c r="M4" s="1">
+        <f>COUNT(C2:C15)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -573,8 +615,20 @@
       <c r="B5">
         <v>15</v>
       </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
       <c r="H5">
         <v>98</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -593,16 +647,31 @@
       <c r="C6">
         <v>32</v>
       </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
       <c r="H6">
         <v>83</v>
       </c>
+      <c r="I6" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1">
+        <f>COUNT(B2:B15)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -611,8 +680,20 @@
       <c r="C7">
         <v>34</v>
       </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
       <c r="H7">
         <v>92</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -632,8 +713,20 @@
       <c r="C8">
         <v>21</v>
       </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
       <c r="H8">
         <v>52</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -649,10 +742,25 @@
       <c r="B9">
         <v>25</v>
       </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
       <c r="H9">
         <v>33</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="I9" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
+      <c r="M9" s="1">
+        <f>COUNTA(K2:K15)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -664,8 +772,20 @@
       <c r="C10">
         <v>12</v>
       </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
       <c r="H10">
         <v>8</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -687,17 +807,44 @@
       <c r="C11">
         <v>11</v>
       </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
       <c r="H11">
         <v>42</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="I11" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
+      <c r="M11" s="1">
+        <f>COUNTIF(H2:H15, "&gt;=70")</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
       <c r="H12">
         <v>49</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -719,13 +866,28 @@
       <c r="C13">
         <v>27</v>
       </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
       <c r="H13">
         <v>39</v>
       </c>
+      <c r="I13" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
       <c r="K13" t="s">
         <v>13</v>
       </c>
-      <c r="M13" s="2"/>
+      <c r="M13" s="2">
+        <f>COUNTIF(H2:H15, 8)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -734,8 +896,20 @@
       <c r="C14">
         <v>29</v>
       </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
       <c r="H14">
         <v>90</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -757,16 +931,31 @@
       <c r="C15">
         <v>9</v>
       </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
       <c r="H15">
         <v>80</v>
       </c>
+      <c r="I15" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" t="s">
         <v>13</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1">
+        <f>COUNTIFS(B2:B15, "&gt;=25", C2:C15, "&lt;=20")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M16" s="1" t="s">
@@ -777,7 +966,22 @@
       <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="1"/>
+      <c r="B17">
+        <f>SUM(B2:B15)</f>
+        <v>210</v>
+      </c>
+      <c r="C17">
+        <f>SUM(C2:C15)</f>
+        <v>268</v>
+      </c>
+      <c r="D17">
+        <f>SUM(D2:D15)</f>
+        <v>478</v>
+      </c>
+      <c r="M17" s="1">
+        <f>SUMIF(H2:H15, "&gt;=70", F2:F15)</f>
+        <v>328</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M18" s="1" t="s">
@@ -785,7 +989,10 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M19" s="1"/>
+      <c r="M19" s="1">
+        <f>SUMIFS(F2:F15, H2:H15, "&gt;=70", J2:J15, 1)</f>
+        <v>264</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
